--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-Practitioner.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-Practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -439,7 +439,7 @@
     <t>Practitioner.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -477,7 +477,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -554,7 +554,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -809,715 +809,706 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:TelematikID</t>
+  </si>
+  <si>
+    <t>TelematikID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
+</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:LANR</t>
+  </si>
+  <si>
+    <t>LANR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-lanr}
+</t>
+  </si>
+  <si>
+    <t>Practitioner.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether this practitioner's record is in active use</t>
+  </si>
+  <si>
+    <t>Whether this practitioner's record is in active use.</t>
+  </si>
+  <si>
+    <t>If the practitioner is not in use by one organization, then it should mark the period on the PractitonerRole with an end date (even if they are active) as they may be active in another role.</t>
+  </si>
+  <si>
+    <t>Need to be able to mark a practitioner record as not to be used because it was created in error.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>./statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Practitioner.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumanName {http://fhir.de/StructureDefinition/humanname-de-basis}
+</t>
+  </si>
+  <si>
+    <t>The name(s) associated with the practitioner</t>
+  </si>
+  <si>
+    <t>The name(s) associated with the practitioner.</t>
+  </si>
+  <si>
+    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  ++In general, select the value to be used in the ResourceReference.display based on this:++1. There is more than 1 name+2. Use = usual+3. Period is current to the date of the usage+4. Use = official+5. Other order as decided by internal business rules.</t>
+  </si>
+  <si>
+    <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
+  </si>
+  <si>
+    <t>XCN Components</t>
+  </si>
+  <si>
+    <t>./name</t>
+  </si>
+  <si>
+    <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
+  </si>
+  <si>
+    <t>Practitioner.name.id</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Practitioner.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Familienname</t>
+  </si>
+  <si>
+    <t>Der vollständige Familienname, einschließlich aller Vorsatz- und Zusatzwörter, mit Leerzeichen getrennt.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>./FamilyName</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family.id</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family.extension:namenszusatz</t>
+  </si>
+  <si>
+    <t>namenszusatz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/humanname-namenszusatz}
+</t>
+  </si>
+  <si>
+    <t>Namenszusatz gemäß VSDM (Versichertenstammdatenmanagement, "eGK")</t>
+  </si>
+  <si>
+    <t>Namenszusatz als Bestandteil das Nachnamens, wie in VSDM (Versichertenstammdatenmanagement, "eGK") definiert.
+Beispiele: Gräfin, Prinz oder Fürst</t>
+  </si>
+  <si>
+    <t>Die Extension wurde erstellt aufgrund der Anforderung, die auf der eGK vorhandenen Patientenstammdaten in FHIR abbilden zu können. Auf der eGK werden die Namensbestandteile "Namenszusatz" und "Vorsatzwort" getrennt vom Nachnamen gespeichert. Anhand der Liste der zulässigen Namenszusätze ist deutlich erkennbar, dass es sich hierbei sinngemäß um Adelstitel handelt.
+Das Vorsatzwort kann durch die Core-Extension own-prefix	(Canonical: http://hl7.org/fhir/StructureDefinition/humanname-own-prefix) abgebildet werden, für den Namenszusatz ergibt sich jedoch die Notwendikeit einer nationalen Extension, da in andern Ländern Adelstitel entweder gar nicht oder als reguläres Namenspräfix erfasst werden.</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family.extension:nachname</t>
+  </si>
+  <si>
+    <t>nachname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-own-name}
+</t>
+  </si>
+  <si>
+    <t>Nachname ohne Vor- und Zusätze</t>
+  </si>
+  <si>
+    <t>Nachname ohne Vor- und Zusätze.
+Dient z.B. der alphabetischen Einordnung des Namens.</t>
+  </si>
+  <si>
+    <t>If the person's surname has legally changed to become (or incorporate) the surname of the person's partner or spouse, this is the person's surname immediately prior to such change. Often this is the person's "maiden name".</t>
+  </si>
+  <si>
+    <t>FN.3</t>
+  </si>
+  <si>
+    <t>ENXP where Qualifiers = (BR)</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family.extension:vorsatzwort</t>
+  </si>
+  <si>
+    <t>vorsatzwort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-own-prefix}
+</t>
+  </si>
+  <si>
+    <t>Vorsatzwort</t>
+  </si>
+  <si>
+    <t>Vorsatzwort wie z.B.: von, van, zu
+Vgl. auch VSDM-Spezifikation der Gematik (Versichertenstammdatenmanagement, "eGK")</t>
+  </si>
+  <si>
+    <t>An example of a voorvoegsel is the "van" in "Ludwig van Beethoven". Since the voorvoegsel doesn't sort completely alphabetically, it is reasonable to specify it as a separate sub-component.</t>
+  </si>
+  <si>
+    <t>FN.2</t>
+  </si>
+  <si>
+    <t>ENXP where Qualifiers = (VV, R)</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family.value</t>
+  </si>
+  <si>
+    <t>Primitive value for string</t>
+  </si>
+  <si>
+    <t>1048576</t>
+  </si>
+  <si>
+    <t>string.value</t>
+  </si>
+  <si>
+    <t>Practitioner.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Vorname</t>
+  </si>
+  <si>
+    <t>Vorname der Person</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>./GivenNames</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix</t>
+  </si>
+  <si>
+    <t>Namensteile vor dem Vornamen</t>
+  </si>
+  <si>
+    <t>Namensteile vor dem Vornamen, z.B. akademischer Titel.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>./TitleCode</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix.id</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix.extension:prefix-qualifier</t>
+  </si>
+  <si>
+    <t>prefix-qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {iso21090-EN-qualifier}
+</t>
+  </si>
+  <si>
+    <t>LS | AC | NB | PR | HON | BR | AD | SP | MID | CL | IN | VV</t>
+  </si>
+  <si>
+    <t>Spezialisierung der Art des Präfixes, z.B. "AC" für Akademische Titel</t>
+  </si>
+  <si>
+    <t>Used to indicate additional information about the name part and how it should be used.</t>
+  </si>
+  <si>
+    <t>ENXP.qualifier</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix.value</t>
+  </si>
+  <si>
+    <t>Practitioner.name.suffix</t>
+  </si>
+  <si>
+    <t>Namensteile nach dem Nachnamen</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>Practitioner.name.period</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
     <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
 Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
   </si>
   <si>
-    <t>Identifier.period</t>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t>XPN.13 + XPN.14</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
+    <t>Practitioner.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
+    <t>A contact detail for the practitioner (that apply to all roles)</t>
+  </si>
+  <si>
+    <t>A contact detail for the practitioner, e.g. a telephone number or an email address.</t>
+  </si>
+  <si>
+    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and to help with identification.  These typically will have home numbers, or mobile numbers that are not role specific.</t>
+  </si>
+  <si>
+    <t>Need to know how to reach a practitioner independent to any roles the practitioner may have.</t>
+  </si>
+  <si>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>PRT-15, STF-10, ROL-12</t>
+  </si>
+  <si>
+    <t>./telecom</t>
+  </si>
+  <si>
+    <t>./ContactPoints</t>
+  </si>
+  <si>
+    <t>Practitioner.address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address
+</t>
+  </si>
+  <si>
+    <t>Address(es) of the practitioner that are not role specific (typically home address)</t>
+  </si>
+  <si>
+    <t>Address(es) of the practitioner that are not role specific (typically home address). +Work addresses are not typically entered in this property as they are usually role dependent.</t>
+  </si>
+  <si>
+    <t>The PractitionerRole does not have an address value on it, as it is expected that the location property be used for this purpose (which has an address).</t>
+  </si>
+  <si>
+    <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
+  </si>
+  <si>
+    <t>ORC-24, STF-11, ROL-11, PRT-14</t>
+  </si>
+  <si>
+    <t>./addr</t>
+  </si>
+  <si>
+    <t>./Addresses</t>
+  </si>
+  <si>
+    <t>Practitioner.gender</t>
+  </si>
+  <si>
+    <t>male | female | other | unknown</t>
+  </si>
+  <si>
+    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
+  </si>
+  <si>
+    <t>Needed to address the person correctly.</t>
+  </si>
+  <si>
+    <t>The gender of a person used for administrative purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
+  </si>
+  <si>
+    <t>STF-5</t>
+  </si>
+  <si>
+    <t>./administrativeGender</t>
+  </si>
+  <si>
+    <t>./GenderCode</t>
+  </si>
+  <si>
+    <t>Practitioner.birthDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>The date  on which the practitioner was born</t>
+  </si>
+  <si>
+    <t>The date of birth for the practitioner.</t>
+  </si>
+  <si>
+    <t>Needed for identification.</t>
+  </si>
+  <si>
+    <t>STF-6</t>
+  </si>
+  <si>
+    <t>./birthTime</t>
+  </si>
+  <si>
+    <t>(not represented in ServD)</t>
+  </si>
+  <si>
+    <t>Practitioner.photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Image of the person</t>
+  </si>
+  <si>
+    <t>Image of the person.</t>
+  </si>
+  <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
+    <t>Many EHR systems have the capability to capture an image of patients and personnel. Fits with newer social media usage too.</t>
+  </si>
+  <si>
+    <t>att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>ED/RP</t>
+  </si>
+  <si>
+    <t>./subjectOf/ObservationEvent[code="photo"]/value</t>
+  </si>
+  <si>
+    <t>./ImageURI (only supports the URI reference)</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Certification, licenses, or training pertaining to the provision of care</t>
+  </si>
+  <si>
+    <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
+  </si>
+  <si>
+    <t>CER?</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].code</t>
+  </si>
+  <si>
+    <t>./Qualifications</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.identifier</t>
+  </si>
+  <si>
+    <t>An identifier for this qualification for the practitioner</t>
+  </si>
+  <si>
+    <t>An identifier that applies to this person's qualification in this role.</t>
+  </si>
+  <si>
+    <t>Often, specific identities are assigned for the qualification.</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].id</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code</t>
+  </si>
+  <si>
+    <t>Coded representation of the qualification</t>
+  </si>
+  <si>
+    <t>Coded representation of the qualification.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
+    <t>https://gematik.de/fhir/directory/ValueSet/PractitionerQualificationVS</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
+    <t>./Qualifications.Value</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid.</t>
+  </si>
+  <si>
+    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].effectiveTime</t>
+  </si>
+  <si>
+    <t>./Qualifications.StartDate and ./Qualifications.EndDate</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.issuer</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:TelematikID</t>
-  </si>
-  <si>
-    <t>TelematikID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-telematik-id}
-</t>
-  </si>
-  <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
-    <t>Practitioner.identifier:LANR</t>
-  </si>
-  <si>
-    <t>LANR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-lanr}
-</t>
-  </si>
-  <si>
-    <t>Practitioner.active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>Whether this practitioner's record is in active use</t>
-  </si>
-  <si>
-    <t>Whether this practitioner's record is in active use.</t>
-  </si>
-  <si>
-    <t>If the practitioner is not in use by one organization, then it should mark the period on the PractitonerRole with an end date (even if they are active) as they may be active in another role.</t>
-  </si>
-  <si>
-    <t>Need to be able to mark a practitioner record as not to be used because it was created in error.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>./statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Practitioner.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HumanName {http://fhir.de/StructureDefinition/humanname-de-basis}
-</t>
-  </si>
-  <si>
-    <t>Personenname</t>
-  </si>
-  <si>
-    <t>Personenname mit in Deutschland üblichen Erweiterungen</t>
-  </si>
-  <si>
-    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts may or may not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
-  </si>
-  <si>
-    <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-hum-1:Wenn die Extension 'namenszusatz' verwendet wird, dann muss der vollständige Name im Attribut 'family' angegeben werden {family.extension('http://fhir.de/StructureDefinition/humanname-namenszusatz').empty() or family.hasValue()}hum-2:Wenn die Extension 'nachname' verwendet wird, dann muss der vollständige Name im Attribut 'family' angegeben werden {family.extension('http://hl7.org/fhir/StructureDefinition/humanname-own-name').empty() or family.hasValue()}hum-3:Wenn die Extension 'vorsatzwort' verwendet wird, dann muss der vollständige Name im Attribut 'family' angegeben werden {family.extension('http://hl7.org/fhir/StructureDefinition/humanname-own-prefix').empty() or family.hasValue()}hum-4:Wenn die Extension 'prefix-qualifier' verwendet wird, dann muss ein Namenspräfix im Attribut 'prefix' angegeben werden {prefix.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-EN-qualifier').empty() or $this.hasValue())}</t>
-  </si>
-  <si>
-    <t>XCN Components</t>
-  </si>
-  <si>
-    <t>./name</t>
-  </si>
-  <si>
-    <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
-  </si>
-  <si>
-    <t>Practitioner.name.id</t>
-  </si>
-  <si>
-    <t>Practitioner.name.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./NamePurpose</t>
-  </si>
-  <si>
-    <t>Practitioner.name.text</t>
-  </si>
-  <si>
-    <t>Text representation of the full name</t>
-  </si>
-  <si>
-    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
-  </si>
-  <si>
-    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
-  </si>
-  <si>
-    <t>A renderable, unencoded form.</t>
-  </si>
-  <si>
-    <t>HumanName.text</t>
-  </si>
-  <si>
-    <t>implied by XPN.11</t>
-  </si>
-  <si>
-    <t>./formatted</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">surname
-</t>
-  </si>
-  <si>
-    <t>Familienname</t>
-  </si>
-  <si>
-    <t>Der vollständige Familienname, einschließlich aller Vorsatz- und Zusatzwörter, mit Leerzeichen getrennt.</t>
-  </si>
-  <si>
-    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
-  </si>
-  <si>
-    <t>HumanName.family</t>
-  </si>
-  <si>
-    <t>XPN.1/FN.1</t>
-  </si>
-  <si>
-    <t>./part[partType = FAM]</t>
-  </si>
-  <si>
-    <t>./FamilyName</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family.id</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family.extension:namenszusatz</t>
-  </si>
-  <si>
-    <t>namenszusatz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://fhir.de/StructureDefinition/humanname-namenszusatz}
-</t>
-  </si>
-  <si>
-    <t>Namenszusatz gemäß VSDM (Versichertenstammdatenmanagement, "eGK")</t>
-  </si>
-  <si>
-    <t>Namenszusatz als Bestandteil das Nachnamens, wie in VSDM (Versichertenstammdatenmanagement, "eGK") definiert.
-Beispiele: Gräfin, Prinz oder Fürst</t>
-  </si>
-  <si>
-    <t>Die Extension wurde erstellt aufgrund der Anforderung, die auf der eGK vorhandenen Patientenstammdaten in FHIR abbilden zu können. Auf der eGK werden die Namensbestandteile "Namenszusatz" und "Vorsatzwort" getrennt vom Nachnamen gespeichert. Anhand der Liste der zulässigen Namenszusätze ist deutlich erkennbar, dass es sich hierbei sinngemäß um Adelstitel handelt.
-Das Vorsatzwort kann durch die Core-Extension own-prefix	(Canonical: http://hl7.org/fhir/StructureDefinition/humanname-own-prefix) abgebildet werden, für den Namenszusatz ergibt sich jedoch die Notwendikeit einer nationalen Extension, da in andern Ländern Adelstitel entweder gar nicht oder als reguläres Namenspräfix erfasst werden.</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family.extension:nachname</t>
-  </si>
-  <si>
-    <t>nachname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {humanname-own-name}
-</t>
-  </si>
-  <si>
-    <t>Nachname ohne Vor- und Zusätze</t>
-  </si>
-  <si>
-    <t>Nachname ohne Vor- und Zusätze.
-Dient z.B. der alphabetischen Einordnung des Namens.</t>
-  </si>
-  <si>
-    <t>If the person's surname has legally changed to become (or incorporate) the surname of the person's partner or spouse, this is the person's surname immediately prior to such change. Often this is the person's "maiden name".</t>
-  </si>
-  <si>
-    <t>FN.3</t>
-  </si>
-  <si>
-    <t>ENXP where Qualifiers = (BR)</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family.extension:vorsatzwort</t>
-  </si>
-  <si>
-    <t>vorsatzwort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {humanname-own-prefix}
-</t>
-  </si>
-  <si>
-    <t>Vorsatzwort</t>
-  </si>
-  <si>
-    <t>Vorsatzwort wie z.B.: von, van, zu
-Vgl. auch VSDM-Spezifikation der Gematik (Versichertenstammdatenmanagement, "eGK")</t>
-  </si>
-  <si>
-    <t>An example of a voorvoegsel is the "van" in "Ludwig van Beethoven". Since the voorvoegsel doesn't sort completely alphabetically, it is reasonable to specify it as a separate sub-component.</t>
-  </si>
-  <si>
-    <t>FN.2</t>
-  </si>
-  <si>
-    <t>ENXP where Qualifiers = (VV, R)</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family.value</t>
-  </si>
-  <si>
-    <t>Primitive value for string</t>
-  </si>
-  <si>
-    <t>1048576</t>
-  </si>
-  <si>
-    <t>string.value</t>
-  </si>
-  <si>
-    <t>Practitioner.name.given</t>
-  </si>
-  <si>
-    <t>first name
-middle name</t>
-  </si>
-  <si>
-    <t>Vorname</t>
-  </si>
-  <si>
-    <t>Vorname der Person</t>
-  </si>
-  <si>
-    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
-  </si>
-  <si>
-    <t>HumanName.given</t>
-  </si>
-  <si>
-    <t>XPN.2 + XPN.3</t>
-  </si>
-  <si>
-    <t>./part[partType = GIV]</t>
-  </si>
-  <si>
-    <t>./GivenNames</t>
-  </si>
-  <si>
-    <t>Practitioner.name.prefix</t>
-  </si>
-  <si>
-    <t>Namensteile vor dem Vornamen</t>
-  </si>
-  <si>
-    <t>Namensteile vor dem Vornamen, z.B. akademischer Titel.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>HumanName.prefix</t>
-  </si>
-  <si>
-    <t>XPN.5</t>
-  </si>
-  <si>
-    <t>./part[partType = PFX]</t>
-  </si>
-  <si>
-    <t>./TitleCode</t>
-  </si>
-  <si>
-    <t>Practitioner.name.prefix.id</t>
-  </si>
-  <si>
-    <t>Practitioner.name.prefix.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.name.prefix.extension:prefix-qualifier</t>
-  </si>
-  <si>
-    <t>prefix-qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {iso21090-EN-qualifier}
-</t>
-  </si>
-  <si>
-    <t>LS | AC | NB | PR | HON | BR | AD | SP | MID | CL | IN | VV</t>
-  </si>
-  <si>
-    <t>Spezialisierung der Art des Präfixes, z.B. "AC" für Akademische Titel</t>
-  </si>
-  <si>
-    <t>Used to indicate additional information about the name part and how it should be used.</t>
-  </si>
-  <si>
-    <t>ENXP.qualifier</t>
-  </si>
-  <si>
-    <t>Practitioner.name.prefix.value</t>
-  </si>
-  <si>
-    <t>Practitioner.name.suffix</t>
-  </si>
-  <si>
-    <t>Namensteile nach dem Nachnamen</t>
-  </si>
-  <si>
-    <t>HumanName.suffix</t>
-  </si>
-  <si>
-    <t>XPN/4</t>
-  </si>
-  <si>
-    <t>./part[partType = SFX]</t>
-  </si>
-  <si>
-    <t>Practitioner.name.period</t>
-  </si>
-  <si>
-    <t>Time period when name was/is in use</t>
-  </si>
-  <si>
-    <t>Indicates the period of time when this name was valid for the named person.</t>
-  </si>
-  <si>
-    <t>Allows names to be placed in historical context.</t>
-  </si>
-  <si>
-    <t>HumanName.period</t>
-  </si>
-  <si>
-    <t>XPN.13 + XPN.14</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
-  </si>
-  <si>
-    <t>Practitioner.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>A contact detail for the practitioner (that apply to all roles)</t>
-  </si>
-  <si>
-    <t>A contact detail for the practitioner, e.g. a telephone number or an email address.</t>
-  </si>
-  <si>
-    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and to help with identification.  These typically will have home numbers, or mobile numbers that are not role specific.</t>
-  </si>
-  <si>
-    <t>Need to know how to reach a practitioner independent to any roles the practitioner may have.</t>
-  </si>
-  <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>PRT-15, STF-10, ROL-12</t>
-  </si>
-  <si>
-    <t>./telecom</t>
-  </si>
-  <si>
-    <t>./ContactPoints</t>
-  </si>
-  <si>
-    <t>Practitioner.address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address
-</t>
-  </si>
-  <si>
-    <t>Address(es) of the practitioner that are not role specific (typically home address)</t>
-  </si>
-  <si>
-    <t>Address(es) of the practitioner that are not role specific (typically home address). -Work addresses are not typically entered in this property as they are usually role dependent.</t>
-  </si>
-  <si>
-    <t>The PractitionerRole does not have an address value on it, as it is expected that the location property be used for this purpose (which has an address).</t>
-  </si>
-  <si>
-    <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
-  </si>
-  <si>
-    <t>ORC-24, STF-11, ROL-11, PRT-14</t>
-  </si>
-  <si>
-    <t>./addr</t>
-  </si>
-  <si>
-    <t>./Addresses</t>
-  </si>
-  <si>
-    <t>Practitioner.gender</t>
-  </si>
-  <si>
-    <t>male | female | other | unknown</t>
-  </si>
-  <si>
-    <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
-  </si>
-  <si>
-    <t>Needed to address the person correctly.</t>
-  </si>
-  <si>
-    <t>The gender of a person used for administrative purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
-  </si>
-  <si>
-    <t>STF-5</t>
-  </si>
-  <si>
-    <t>./administrativeGender</t>
-  </si>
-  <si>
-    <t>./GenderCode</t>
-  </si>
-  <si>
-    <t>Practitioner.birthDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date
-</t>
-  </si>
-  <si>
-    <t>The date  on which the practitioner was born</t>
-  </si>
-  <si>
-    <t>The date of birth for the practitioner.</t>
-  </si>
-  <si>
-    <t>Needed for identification.</t>
-  </si>
-  <si>
-    <t>STF-6</t>
-  </si>
-  <si>
-    <t>./birthTime</t>
-  </si>
-  <si>
-    <t>(not represented in ServD)</t>
-  </si>
-  <si>
-    <t>Practitioner.photo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attachment
-</t>
-  </si>
-  <si>
-    <t>Image of the person</t>
-  </si>
-  <si>
-    <t>Image of the person.</t>
-  </si>
-  <si>
-    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
-  </si>
-  <si>
-    <t>Many EHR systems have the capability to capture an image of patients and personnel. Fits with newer social media usage too.</t>
-  </si>
-  <si>
-    <t>att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>ED/RP</t>
-  </si>
-  <si>
-    <t>./subjectOf/ObservationEvent[code="photo"]/value</t>
-  </si>
-  <si>
-    <t>./ImageURI (only supports the URI reference)</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Certification, licenses, or training pertaining to the provision of care</t>
-  </si>
-  <si>
-    <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
-  </si>
-  <si>
-    <t>CER?</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].code</t>
-  </si>
-  <si>
-    <t>./Qualifications</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.identifier</t>
-  </si>
-  <si>
-    <t>An identifier for this qualification for the practitioner</t>
-  </si>
-  <si>
-    <t>An identifier that applies to this person's qualification in this role.</t>
-  </si>
-  <si>
-    <t>Often, specific identities are assigned for the qualification.</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].id</t>
-  </si>
-  <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code</t>
-  </si>
-  <si>
-    <t>Coded representation of the qualification</t>
-  </si>
-  <si>
-    <t>Coded representation of the qualification.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>Specific qualification the practitioner has to provide a service.</t>
-  </si>
-  <si>
-    <t>https://gematik.de/fhir/directory/ValueSet/PractitionerQualificationVS</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>./Qualifications.Value</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period</t>
-  </si>
-  <si>
-    <t>Period during which the qualification is valid</t>
-  </si>
-  <si>
-    <t>Period during which the qualification is valid.</t>
-  </si>
-  <si>
-    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
-  </si>
-  <si>
-    <t>DR</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].effectiveTime</t>
-  </si>
-  <si>
-    <t>./Qualifications.StartDate and ./Qualifications.EndDate</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
   </si>
   <si>
     <t>.playingEntity.playingRole[classCode=QUAL].scoper</t>
@@ -4515,7 +4506,7 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>100</v>
@@ -4799,9 +4790,7 @@
       <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>255</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4850,7 +4839,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4859,19 +4848,19 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4879,10 +4868,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4905,16 +4894,16 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4964,7 +4953,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4973,19 +4962,19 @@
         <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4993,13 +4982,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -5021,13 +5010,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
@@ -5109,13 +5098,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>77</v>
@@ -5137,13 +5126,13 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
@@ -5225,10 +5214,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5251,26 +5240,26 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="P30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q30" t="s" s="2">
-        <v>285</v>
-      </c>
       <c r="R30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5314,7 +5303,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5332,21 +5321,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5369,19 +5358,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5430,7 +5419,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5442,16 +5431,16 @@
         <v>150</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5459,10 +5448,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5571,10 +5560,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5685,10 +5674,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5714,16 +5703,16 @@
         <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5751,10 +5740,10 @@
         <v>217</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5772,7 +5761,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5787,13 +5776,13 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5801,10 +5790,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5830,16 +5819,16 @@
         <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5888,7 +5877,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5903,10 +5892,10 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5917,14 +5906,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5946,13 +5935,13 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6002,7 +5991,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6017,13 +6006,13 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6031,10 +6020,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6143,10 +6132,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6257,13 +6246,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>108</v>
@@ -6285,16 +6274,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6373,13 +6362,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>108</v>
@@ -6401,16 +6390,16 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6475,10 +6464,10 @@
         <v>117</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6489,13 +6478,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>108</v>
@@ -6517,16 +6506,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6591,10 +6580,10 @@
         <v>117</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6605,10 +6594,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6634,10 +6623,10 @@
         <v>102</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6661,7 +6650,7 @@
         <v>77</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="X42" t="s" s="2">
         <v>77</v>
@@ -6688,7 +6677,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6717,14 +6706,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6746,13 +6735,13 @@
         <v>102</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6802,7 +6791,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6817,13 +6806,13 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6831,10 +6820,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6860,13 +6849,13 @@
         <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6916,7 +6905,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6931,13 +6920,13 @@
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6945,10 +6934,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7057,10 +7046,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7171,13 +7160,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>108</v>
@@ -7199,16 +7188,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7276,7 +7265,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7287,10 +7276,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7316,10 +7305,10 @@
         <v>102</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7343,7 +7332,7 @@
         <v>77</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="X48" t="s" s="2">
         <v>77</v>
@@ -7370,7 +7359,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7399,10 +7388,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7428,13 +7417,13 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7484,7 +7473,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7499,10 +7488,10 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7513,10 +7502,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7542,16 +7531,16 @@
         <v>252</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7600,7 +7589,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7612,16 +7601,16 @@
         <v>150</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7629,10 +7618,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7655,19 +7644,19 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7716,7 +7705,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7728,16 +7717,16 @@
         <v>150</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7745,10 +7734,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7771,19 +7760,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7832,7 +7821,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7847,13 +7836,13 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7861,10 +7850,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7890,14 +7879,14 @@
         <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7925,10 +7914,10 @@
         <v>217</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7946,7 +7935,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7961,13 +7950,13 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7975,10 +7964,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8001,17 +7990,17 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8060,7 +8049,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8075,13 +8064,13 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8089,10 +8078,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8115,19 +8104,19 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8176,7 +8165,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8188,16 +8177,16 @@
         <v>150</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8205,10 +8194,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8231,13 +8220,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8288,7 +8277,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8303,13 +8292,13 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8317,10 +8306,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8429,10 +8418,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8543,14 +8532,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8572,10 +8561,10 @@
         <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>112</v>
@@ -8630,7 +8619,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8659,10 +8648,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8688,14 +8677,14 @@
         <v>200</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8744,7 +8733,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8759,13 +8748,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8773,10 +8762,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8802,13 +8791,13 @@
         <v>223</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8836,11 +8825,9 @@
       <c r="X61" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="Y61" t="s" s="2">
-        <v>466</v>
-      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8858,7 +8845,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>88</v>
@@ -8873,13 +8860,13 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8887,10 +8874,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8916,16 +8903,16 @@
         <v>252</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8974,7 +8961,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8986,16 +8973,16 @@
         <v>150</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>257</v>
+        <v>388</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9003,10 +8990,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9029,16 +9016,16 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>478</v>
+        <v>260</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9088,7 +9075,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9100,13 +9087,13 @@
         <v>150</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>267</v>
+        <v>476</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -9117,10 +9104,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9146,16 +9133,16 @@
         <v>223</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9204,7 +9191,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9219,13 +9206,13 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
